--- a/Design Files/Remote_Sensor_Unit/BOM/Client_BOM_Remote_Sensor_Unit.xlsx
+++ b/Design Files/Remote_Sensor_Unit/BOM/Client_BOM_Remote_Sensor_Unit.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="412">
   <si>
     <t>Component list</t>
   </si>
@@ -1137,12 +1137,6 @@
     <t>4.7pF</t>
   </si>
   <si>
-    <t>BAT54CW</t>
-  </si>
-  <si>
-    <t>100MHz</t>
-  </si>
-  <si>
     <t>3.3uH</t>
   </si>
   <si>
@@ -1158,9 +1152,6 @@
     <t>1.6nH</t>
   </si>
   <si>
-    <t>RED</t>
-  </si>
-  <si>
     <t>TEST POINT</t>
   </si>
   <si>
@@ -1248,12 +1239,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Alternate Part Number</t>
-  </si>
-  <si>
-    <t>Bill of Materials for Project [Remote_Sensor_Unit.PrjPcb]</t>
-  </si>
-  <si>
     <t>Remote_Sensor_Unit</t>
   </si>
   <si>
@@ -1269,10 +1254,7 @@
     <t>Battery</t>
   </si>
   <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
+    <t>Bill of Materials for Project [Remote_Sensor_Unit]</t>
   </si>
 </sst>
 </file>
@@ -1414,9 +1396,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1448,7 +1430,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1656,40 +1638,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1846,9 +1799,10 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1858,22 +1812,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1899,13 +1845,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -2213,7 +2159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2222,15 +2168,15 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="29.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="29.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2239,14 +2185,12 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-    </row>
-    <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+    </row>
+    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="43"/>
@@ -2255,18 +2199,16 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="52" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="40"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L2" s="40"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="44"/>
@@ -2275,18 +2217,16 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="53" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="61"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L3" s="62"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="44"/>
@@ -2295,18 +2235,16 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="54" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="62"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L4" s="63"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="44"/>
@@ -2318,15 +2256,13 @@
         <v>5</v>
       </c>
       <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="62"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L5" s="63"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="45"/>
@@ -2334,15 +2270,13 @@
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="62"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L6" s="63"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="46"/>
@@ -2350,15 +2284,13 @@
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
       <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="62"/>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="63"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="47"/>
@@ -2366,15 +2298,13 @@
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
       <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="62"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="63"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -2395,28 +2325,22 @@
         <v>251</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>409</v>
-      </c>
-      <c r="I9" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>406</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>416</v>
+      <c r="I9" s="30" t="s">
+        <v>403</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="K9" s="51" t="s">
+        <v>404</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="M9" s="51" t="s">
-        <v>407</v>
-      </c>
-      <c r="N9" s="29" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="50">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2425,30 +2349,28 @@
       <c r="C10" s="56" t="s">
         <v>357</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="36" t="s">
+      <c r="E10" s="65"/>
+      <c r="F10" s="64" t="s">
         <v>196</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36">
-        <v>1</v>
-      </c>
-      <c r="M10" s="37">
-        <f>L10*5</f>
-        <v>5</v>
-      </c>
-      <c r="N10" s="36"/>
-    </row>
-    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="65"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="65" t="s">
+        <v>408</v>
+      </c>
+      <c r="J10" s="64">
+        <v>1</v>
+      </c>
+      <c r="K10" s="65">
+        <f>J10*5</f>
+        <v>5</v>
+      </c>
+      <c r="L10" s="64"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="50">
         <f t="shared" ref="B11:B91" si="0">ROW(B11) - ROW($B$9)</f>
@@ -2469,24 +2391,22 @@
       <c r="G11" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38" t="s">
+      <c r="H11" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J11" s="39" t="s">
+      <c r="I11" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38">
-        <v>1</v>
-      </c>
-      <c r="M11" s="39">
-        <f t="shared" ref="M11" si="1">L11*5</f>
-        <v>5</v>
-      </c>
-      <c r="N11" s="38"/>
-    </row>
-    <row r="12" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="38">
+        <v>1</v>
+      </c>
+      <c r="K11" s="39">
+        <f t="shared" ref="K11" si="1">J11*5</f>
+        <v>5</v>
+      </c>
+      <c r="L11" s="38"/>
+    </row>
+    <row r="12" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="50">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2507,24 +2427,22 @@
       <c r="G12" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36" t="s">
+      <c r="H12" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="I12" s="37" t="s">
         <v>359</v>
       </c>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36">
+      <c r="J12" s="36">
         <v>22</v>
       </c>
-      <c r="M12" s="37">
-        <f>L12*5</f>
+      <c r="K12" s="37">
+        <f>J12*5</f>
         <v>110</v>
       </c>
-      <c r="N12" s="36"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="36"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="50">
         <f t="shared" si="0"/>
@@ -2545,24 +2463,22 @@
       <c r="G13" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38" t="s">
+      <c r="H13" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="I13" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38">
+      <c r="J13" s="38">
         <v>7</v>
       </c>
-      <c r="M13" s="39">
-        <f t="shared" ref="M13" si="2">L13*5</f>
+      <c r="K13" s="39">
+        <f t="shared" ref="K13" si="2">J13*5</f>
         <v>35</v>
       </c>
-      <c r="N13" s="38"/>
-    </row>
-    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="38"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="50">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2583,24 +2499,22 @@
       <c r="G14" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36" t="s">
+      <c r="H14" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J14" s="37" t="s">
+      <c r="I14" s="37" t="s">
         <v>361</v>
       </c>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36">
-        <v>1</v>
-      </c>
-      <c r="M14" s="37">
-        <f>L14*5</f>
-        <v>5</v>
-      </c>
-      <c r="N14" s="36"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="36">
+        <v>1</v>
+      </c>
+      <c r="K14" s="37">
+        <f>J14*5</f>
+        <v>5</v>
+      </c>
+      <c r="L14" s="36"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="50">
         <f t="shared" si="0"/>
@@ -2621,24 +2535,22 @@
       <c r="G15" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38" t="s">
+      <c r="H15" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="J15" s="39" t="s">
+      <c r="I15" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38">
+      <c r="J15" s="38">
         <v>8</v>
       </c>
-      <c r="M15" s="39">
-        <f t="shared" ref="M15" si="3">L15*5</f>
+      <c r="K15" s="39">
+        <f t="shared" ref="K15" si="3">J15*5</f>
         <v>40</v>
       </c>
-      <c r="N15" s="38"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="38"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="50">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -2659,24 +2571,22 @@
       <c r="G16" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36" t="s">
+      <c r="H16" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="I16" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36">
-        <v>1</v>
-      </c>
-      <c r="M16" s="37">
-        <f>L16*5</f>
-        <v>5</v>
-      </c>
-      <c r="N16" s="36"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="36">
+        <v>1</v>
+      </c>
+      <c r="K16" s="37">
+        <f>J16*5</f>
+        <v>5</v>
+      </c>
+      <c r="L16" s="36"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="50">
         <f t="shared" si="0"/>
@@ -2697,24 +2607,22 @@
       <c r="G17" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38" t="s">
+      <c r="H17" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="J17" s="39" t="s">
+      <c r="I17" s="39" t="s">
         <v>364</v>
       </c>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38">
-        <v>1</v>
-      </c>
-      <c r="M17" s="39">
-        <f t="shared" ref="M17" si="4">L17*5</f>
-        <v>5</v>
-      </c>
-      <c r="N17" s="38"/>
-    </row>
-    <row r="18" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="38">
+        <v>1</v>
+      </c>
+      <c r="K17" s="39">
+        <f t="shared" ref="K17" si="4">J17*5</f>
+        <v>5</v>
+      </c>
+      <c r="L17" s="38"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="50">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -2735,24 +2643,22 @@
       <c r="G18" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36" t="s">
+      <c r="H18" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J18" s="37" t="s">
+      <c r="I18" s="37" t="s">
         <v>365</v>
       </c>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36">
+      <c r="J18" s="36">
         <v>3</v>
       </c>
-      <c r="M18" s="37">
-        <f>L18*5</f>
+      <c r="K18" s="37">
+        <f>J18*5</f>
         <v>15</v>
       </c>
-      <c r="N18" s="36"/>
-    </row>
-    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="36"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="50">
         <f t="shared" si="0"/>
@@ -2773,24 +2679,22 @@
       <c r="G19" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38" t="s">
+      <c r="H19" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J19" s="39" t="s">
+      <c r="I19" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38">
-        <v>1</v>
-      </c>
-      <c r="M19" s="39">
-        <f t="shared" ref="M19" si="5">L19*5</f>
-        <v>5</v>
-      </c>
-      <c r="N19" s="38"/>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="38">
+        <v>1</v>
+      </c>
+      <c r="K19" s="39">
+        <f t="shared" ref="K19" si="5">J19*5</f>
+        <v>5</v>
+      </c>
+      <c r="L19" s="38"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="50">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -2811,24 +2715,22 @@
       <c r="G20" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36" t="s">
+      <c r="H20" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="I20" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36">
+      <c r="J20" s="36">
         <v>2</v>
       </c>
-      <c r="M20" s="37">
-        <f>L20*5</f>
+      <c r="K20" s="37">
+        <f>J20*5</f>
         <v>10</v>
       </c>
-      <c r="N20" s="36"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="36"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="50">
         <f t="shared" si="0"/>
@@ -2849,24 +2751,22 @@
       <c r="G21" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38" t="s">
+      <c r="H21" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J21" s="39" t="s">
+      <c r="I21" s="39" t="s">
         <v>368</v>
       </c>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38">
-        <v>1</v>
-      </c>
-      <c r="M21" s="39">
-        <f t="shared" ref="M21" si="6">L21*5</f>
-        <v>5</v>
-      </c>
-      <c r="N21" s="38"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="38">
+        <v>1</v>
+      </c>
+      <c r="K21" s="39">
+        <f t="shared" ref="K21" si="6">J21*5</f>
+        <v>5</v>
+      </c>
+      <c r="L21" s="38"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="50">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -2887,24 +2787,22 @@
       <c r="G22" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36" t="s">
+      <c r="H22" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J22" s="37" t="s">
+      <c r="I22" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36">
-        <v>1</v>
-      </c>
-      <c r="M22" s="37">
-        <f>L22*5</f>
-        <v>5</v>
-      </c>
-      <c r="N22" s="36"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="36">
+        <v>1</v>
+      </c>
+      <c r="K22" s="37">
+        <f>J22*5</f>
+        <v>5</v>
+      </c>
+      <c r="L22" s="36"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="50">
         <f t="shared" si="0"/>
@@ -2925,24 +2823,22 @@
       <c r="G23" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38" t="s">
+      <c r="H23" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="I23" s="39" t="s">
         <v>370</v>
       </c>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38">
-        <v>1</v>
-      </c>
-      <c r="M23" s="39">
-        <f t="shared" ref="M23" si="7">L23*5</f>
-        <v>5</v>
-      </c>
-      <c r="N23" s="38"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="38">
+        <v>1</v>
+      </c>
+      <c r="K23" s="39">
+        <f t="shared" ref="K23" si="7">J23*5</f>
+        <v>5</v>
+      </c>
+      <c r="L23" s="38"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="50">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -2963,24 +2859,22 @@
       <c r="G24" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36" t="s">
+      <c r="H24" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="I24" s="37" t="s">
         <v>371</v>
       </c>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36">
-        <v>1</v>
-      </c>
-      <c r="M24" s="37">
-        <f>L24*5</f>
-        <v>5</v>
-      </c>
-      <c r="N24" s="36"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="36">
+        <v>1</v>
+      </c>
+      <c r="K24" s="37">
+        <f>J24*5</f>
+        <v>5</v>
+      </c>
+      <c r="L24" s="36"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="50">
         <f t="shared" si="0"/>
@@ -3001,24 +2895,22 @@
       <c r="G25" s="39" t="s">
         <v>266</v>
       </c>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38" t="s">
+      <c r="H25" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="J25" s="39" t="s">
-        <v>266</v>
-      </c>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38">
-        <v>1</v>
-      </c>
-      <c r="M25" s="39">
-        <f t="shared" ref="M25" si="8">L25*5</f>
-        <v>5</v>
-      </c>
-      <c r="N25" s="38"/>
-    </row>
-    <row r="26" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I25" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J25" s="38">
+        <v>1</v>
+      </c>
+      <c r="K25" s="39">
+        <f t="shared" ref="K25" si="8">J25*5</f>
+        <v>5</v>
+      </c>
+      <c r="L25" s="38"/>
+    </row>
+    <row r="26" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="50">
         <f>ROW(B26) - ROW($B$9)</f>
@@ -3039,24 +2931,22 @@
       <c r="G26" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36" t="s">
+      <c r="H26" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="J26" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36">
-        <v>1</v>
-      </c>
-      <c r="M26" s="37">
-        <f>L26*5</f>
-        <v>5</v>
-      </c>
-      <c r="N26" s="36"/>
-    </row>
-    <row r="27" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J26" s="36">
+        <v>1</v>
+      </c>
+      <c r="K26" s="37">
+        <f>J26*5</f>
+        <v>5</v>
+      </c>
+      <c r="L26" s="36"/>
+    </row>
+    <row r="27" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="50">
         <f t="shared" si="0"/>
@@ -3077,24 +2967,22 @@
       <c r="G27" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38" t="s">
+      <c r="H27" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="J27" s="39" t="s">
-        <v>268</v>
-      </c>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38">
-        <v>1</v>
-      </c>
-      <c r="M27" s="39">
-        <f t="shared" ref="M27" si="9">L27*5</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="38"/>
-    </row>
-    <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I27" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J27" s="38">
+        <v>1</v>
+      </c>
+      <c r="K27" s="39">
+        <f t="shared" ref="K27" si="9">J27*5</f>
+        <v>5</v>
+      </c>
+      <c r="L27" s="38"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="50">
         <f>ROW(B28) - ROW($B$9)</f>
@@ -3115,24 +3003,22 @@
       <c r="G28" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36" t="s">
+      <c r="H28" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="J28" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36">
+      <c r="I28" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J28" s="36">
         <v>3</v>
       </c>
-      <c r="M28" s="37">
-        <f>L28*5</f>
+      <c r="K28" s="37">
+        <f>J28*5</f>
         <v>15</v>
       </c>
-      <c r="N28" s="36"/>
-    </row>
-    <row r="29" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="36"/>
+    </row>
+    <row r="29" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="50">
         <f t="shared" si="0"/>
@@ -3153,24 +3039,22 @@
       <c r="G29" s="39" t="s">
         <v>270</v>
       </c>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38" t="s">
+      <c r="H29" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="J29" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38">
-        <v>1</v>
-      </c>
-      <c r="M29" s="39">
-        <f t="shared" ref="M29" si="10">L29*5</f>
-        <v>5</v>
-      </c>
-      <c r="N29" s="38"/>
-    </row>
-    <row r="30" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J29" s="38">
+        <v>1</v>
+      </c>
+      <c r="K29" s="39">
+        <f t="shared" ref="K29" si="10">J29*5</f>
+        <v>5</v>
+      </c>
+      <c r="L29" s="38"/>
+    </row>
+    <row r="30" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="50">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -3191,24 +3075,22 @@
       <c r="G30" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36" t="s">
+      <c r="H30" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="J30" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36">
-        <v>1</v>
-      </c>
-      <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>5</v>
-      </c>
-      <c r="N30" s="36"/>
-    </row>
-    <row r="31" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J30" s="36">
+        <v>1</v>
+      </c>
+      <c r="K30" s="37">
+        <f>J30*5</f>
+        <v>5</v>
+      </c>
+      <c r="L30" s="36"/>
+    </row>
+    <row r="31" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="50">
         <f t="shared" si="0"/>
@@ -3229,24 +3111,22 @@
       <c r="G31" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38" t="s">
+      <c r="H31" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="J31" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="K31" s="38"/>
-      <c r="L31" s="38">
+      <c r="I31" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J31" s="38">
         <v>2</v>
       </c>
-      <c r="M31" s="39">
-        <f t="shared" ref="M31" si="11">L31*5</f>
+      <c r="K31" s="39">
+        <f t="shared" ref="K31" si="11">J31*5</f>
         <v>10</v>
       </c>
-      <c r="N31" s="38"/>
-    </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="38"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="50">
         <f>ROW(B32) - ROW($B$9)</f>
@@ -3267,24 +3147,22 @@
       <c r="G32" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36" t="s">
+      <c r="H32" s="36" t="s">
         <v>329</v>
       </c>
-      <c r="J32" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="K32" s="36"/>
-      <c r="L32" s="36">
-        <v>1</v>
-      </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="36"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J32" s="36">
+        <v>1</v>
+      </c>
+      <c r="K32" s="37">
+        <f>J32*5</f>
+        <v>5</v>
+      </c>
+      <c r="L32" s="36"/>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="50">
         <f t="shared" si="0"/>
@@ -3305,24 +3183,22 @@
       <c r="G33" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38" t="s">
+      <c r="H33" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="J33" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="K33" s="38"/>
-      <c r="L33" s="38">
-        <v>1</v>
-      </c>
-      <c r="M33" s="39">
-        <f t="shared" ref="M33" si="12">L33*5</f>
-        <v>5</v>
-      </c>
-      <c r="N33" s="38"/>
-    </row>
-    <row r="34" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I33" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J33" s="38">
+        <v>1</v>
+      </c>
+      <c r="K33" s="39">
+        <f t="shared" ref="K33" si="12">J33*5</f>
+        <v>5</v>
+      </c>
+      <c r="L33" s="38"/>
+    </row>
+    <row r="34" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="50">
         <f>ROW(B34) - ROW($B$9)</f>
@@ -3343,24 +3219,22 @@
       <c r="G34" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36" t="s">
+      <c r="H34" s="36" t="s">
         <v>330</v>
       </c>
-      <c r="J34" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36">
-        <v>1</v>
-      </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
-        <v>5</v>
-      </c>
-      <c r="N34" s="36"/>
-    </row>
-    <row r="35" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J34" s="36">
+        <v>1</v>
+      </c>
+      <c r="K34" s="37">
+        <f>J34*5</f>
+        <v>5</v>
+      </c>
+      <c r="L34" s="36"/>
+    </row>
+    <row r="35" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="50">
         <f t="shared" si="0"/>
@@ -3381,24 +3255,22 @@
       <c r="G35" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38" t="s">
+      <c r="H35" s="38" t="s">
         <v>331</v>
       </c>
-      <c r="J35" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="K35" s="38"/>
-      <c r="L35" s="38">
+      <c r="I35" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J35" s="38">
         <v>2</v>
       </c>
-      <c r="M35" s="39">
-        <f t="shared" ref="M35" si="13">L35*5</f>
+      <c r="K35" s="39">
+        <f t="shared" ref="K35" si="13">J35*5</f>
         <v>10</v>
       </c>
-      <c r="N35" s="38"/>
-    </row>
-    <row r="36" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L35" s="38"/>
+    </row>
+    <row r="36" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="50">
         <f>ROW(B36) - ROW($B$9)</f>
@@ -3419,24 +3291,22 @@
       <c r="G36" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36" t="s">
+      <c r="H36" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="J36" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="K36" s="36"/>
-      <c r="L36" s="36">
+      <c r="I36" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J36" s="36">
         <v>4</v>
       </c>
-      <c r="M36" s="37">
-        <f>L36*5</f>
+      <c r="K36" s="37">
+        <f>J36*5</f>
         <v>20</v>
       </c>
-      <c r="N36" s="36"/>
-    </row>
-    <row r="37" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="36"/>
+    </row>
+    <row r="37" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="50">
         <f t="shared" si="0"/>
@@ -3457,24 +3327,22 @@
       <c r="G37" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38" t="s">
+      <c r="H37" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="J37" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38">
-        <v>1</v>
-      </c>
-      <c r="M37" s="39">
-        <f t="shared" ref="M37" si="14">L37*5</f>
-        <v>5</v>
-      </c>
-      <c r="N37" s="38"/>
-    </row>
-    <row r="38" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I37" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J37" s="38">
+        <v>1</v>
+      </c>
+      <c r="K37" s="39">
+        <f t="shared" ref="K37" si="14">J37*5</f>
+        <v>5</v>
+      </c>
+      <c r="L37" s="38"/>
+    </row>
+    <row r="38" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="50">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -3495,24 +3363,22 @@
       <c r="G38" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36" t="s">
+      <c r="H38" s="36" t="s">
         <v>334</v>
       </c>
-      <c r="J38" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="K38" s="36"/>
-      <c r="L38" s="36">
-        <v>1</v>
-      </c>
-      <c r="M38" s="37">
-        <f>L38*5</f>
-        <v>5</v>
-      </c>
-      <c r="N38" s="36"/>
-    </row>
-    <row r="39" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I38" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J38" s="36">
+        <v>1</v>
+      </c>
+      <c r="K38" s="37">
+        <f>J38*5</f>
+        <v>5</v>
+      </c>
+      <c r="L38" s="36"/>
+    </row>
+    <row r="39" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="50">
         <f t="shared" si="0"/>
@@ -3533,24 +3399,22 @@
       <c r="G39" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38" t="s">
+      <c r="H39" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="J39" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38">
-        <v>1</v>
-      </c>
-      <c r="M39" s="39">
-        <f t="shared" ref="M39" si="15">L39*5</f>
-        <v>5</v>
-      </c>
-      <c r="N39" s="38"/>
-    </row>
-    <row r="40" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I39" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J39" s="38">
+        <v>1</v>
+      </c>
+      <c r="K39" s="39">
+        <f t="shared" ref="K39" si="15">J39*5</f>
+        <v>5</v>
+      </c>
+      <c r="L39" s="38"/>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="50">
         <f>ROW(B40) - ROW($B$9)</f>
@@ -3572,21 +3436,19 @@
         <v>277</v>
       </c>
       <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="K40" s="36"/>
-      <c r="L40" s="36">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f>L40*5</f>
-        <v>5</v>
-      </c>
-      <c r="N40" s="36"/>
-    </row>
-    <row r="41" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I40" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J40" s="36">
+        <v>1</v>
+      </c>
+      <c r="K40" s="37">
+        <f>J40*5</f>
+        <v>5</v>
+      </c>
+      <c r="L40" s="36"/>
+    </row>
+    <row r="41" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="50">
         <f t="shared" si="0"/>
@@ -3607,24 +3469,22 @@
       <c r="G41" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38" t="s">
+      <c r="H41" s="38" t="s">
         <v>336</v>
       </c>
-      <c r="J41" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38">
-        <v>1</v>
-      </c>
-      <c r="M41" s="39">
-        <f t="shared" ref="M41" si="16">L41*5</f>
-        <v>5</v>
-      </c>
-      <c r="N41" s="38"/>
-    </row>
-    <row r="42" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I41" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J41" s="38">
+        <v>1</v>
+      </c>
+      <c r="K41" s="39">
+        <f t="shared" ref="K41" si="16">J41*5</f>
+        <v>5</v>
+      </c>
+      <c r="L41" s="38"/>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="50">
         <f>ROW(B42) - ROW($B$9)</f>
@@ -3645,24 +3505,22 @@
       <c r="G42" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36" t="s">
+      <c r="H42" s="36" t="s">
         <v>337</v>
       </c>
-      <c r="J42" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="K42" s="36"/>
-      <c r="L42" s="36">
+      <c r="I42" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J42" s="36">
         <v>2</v>
       </c>
-      <c r="M42" s="37">
-        <f>L42*5</f>
+      <c r="K42" s="37">
+        <f>J42*5</f>
         <v>10</v>
       </c>
-      <c r="N42" s="36"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L42" s="36"/>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="50">
         <f t="shared" si="0"/>
@@ -3683,24 +3541,22 @@
       <c r="G43" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38" t="s">
+      <c r="H43" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="J43" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="K43" s="38"/>
-      <c r="L43" s="38">
-        <v>1</v>
-      </c>
-      <c r="M43" s="39">
-        <f t="shared" ref="M43" si="17">L43*5</f>
-        <v>5</v>
-      </c>
-      <c r="N43" s="38"/>
-    </row>
-    <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I43" s="39" t="s">
+        <v>372</v>
+      </c>
+      <c r="J43" s="38">
+        <v>1</v>
+      </c>
+      <c r="K43" s="39">
+        <f t="shared" ref="K43" si="17">J43*5</f>
+        <v>5</v>
+      </c>
+      <c r="L43" s="38"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="50">
         <f>ROW(B44) - ROW($B$9)</f>
@@ -3721,24 +3577,22 @@
       <c r="G44" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36" t="s">
+      <c r="H44" s="36" t="s">
         <v>323</v>
       </c>
-      <c r="J44" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="K44" s="36"/>
-      <c r="L44" s="36">
-        <v>1</v>
-      </c>
-      <c r="M44" s="37">
-        <f>L44*5</f>
-        <v>5</v>
-      </c>
-      <c r="N44" s="36"/>
-    </row>
-    <row r="45" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I44" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="J44" s="36">
+        <v>1</v>
+      </c>
+      <c r="K44" s="37">
+        <f>J44*5</f>
+        <v>5</v>
+      </c>
+      <c r="L44" s="36"/>
+    </row>
+    <row r="45" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="50">
         <f t="shared" si="0"/>
@@ -3759,24 +3613,22 @@
       <c r="G45" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38" t="s">
+      <c r="H45" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="J45" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="K45" s="38"/>
-      <c r="L45" s="38">
-        <v>1</v>
-      </c>
-      <c r="M45" s="39">
-        <f t="shared" ref="M45" si="18">L45*5</f>
-        <v>5</v>
-      </c>
-      <c r="N45" s="38"/>
-    </row>
-    <row r="46" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I45" s="39" t="s">
+        <v>374</v>
+      </c>
+      <c r="J45" s="38">
+        <v>1</v>
+      </c>
+      <c r="K45" s="39">
+        <f t="shared" ref="K45" si="18">J45*5</f>
+        <v>5</v>
+      </c>
+      <c r="L45" s="38"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="50">
         <f>ROW(B46) - ROW($B$9)</f>
@@ -3797,24 +3649,22 @@
       <c r="G46" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36" t="s">
+      <c r="H46" s="36" t="s">
         <v>340</v>
       </c>
-      <c r="J46" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36">
-        <v>1</v>
-      </c>
-      <c r="M46" s="37">
-        <f>L46*5</f>
-        <v>5</v>
-      </c>
-      <c r="N46" s="36"/>
-    </row>
-    <row r="47" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I46" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="J46" s="36">
+        <v>1</v>
+      </c>
+      <c r="K46" s="37">
+        <f>J46*5</f>
+        <v>5</v>
+      </c>
+      <c r="L46" s="36"/>
+    </row>
+    <row r="47" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="50">
         <f t="shared" si="0"/>
@@ -3835,24 +3685,22 @@
       <c r="G47" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38" t="s">
+      <c r="H47" s="38" t="s">
         <v>341</v>
       </c>
-      <c r="J47" s="39" t="s">
-        <v>378</v>
-      </c>
-      <c r="K47" s="38"/>
-      <c r="L47" s="38">
-        <v>1</v>
-      </c>
-      <c r="M47" s="39">
-        <f t="shared" ref="M47" si="19">L47*5</f>
-        <v>5</v>
-      </c>
-      <c r="N47" s="38"/>
-    </row>
-    <row r="48" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I47" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="J47" s="38">
+        <v>1</v>
+      </c>
+      <c r="K47" s="39">
+        <f t="shared" ref="K47" si="19">J47*5</f>
+        <v>5</v>
+      </c>
+      <c r="L47" s="38"/>
+    </row>
+    <row r="48" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="50">
         <f>ROW(B48) - ROW($B$9)</f>
@@ -3873,24 +3721,22 @@
       <c r="G48" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36" t="s">
+      <c r="H48" s="36" t="s">
         <v>342</v>
       </c>
-      <c r="J48" s="37" t="s">
-        <v>379</v>
-      </c>
-      <c r="K48" s="36"/>
-      <c r="L48" s="36">
+      <c r="I48" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J48" s="36">
         <v>2</v>
       </c>
-      <c r="M48" s="37">
-        <f>L48*5</f>
+      <c r="K48" s="37">
+        <f>J48*5</f>
         <v>10</v>
       </c>
-      <c r="N48" s="36"/>
-    </row>
-    <row r="49" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L48" s="36"/>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="50">
         <f t="shared" si="0"/>
@@ -3911,58 +3757,58 @@
       <c r="G49" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38" t="s">
+      <c r="H49" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="J49" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38">
-        <v>1</v>
-      </c>
-      <c r="M49" s="39">
-        <f t="shared" ref="M49" si="20">L49*5</f>
-        <v>5</v>
-      </c>
-      <c r="N49" s="38"/>
-    </row>
-    <row r="50" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I49" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J49" s="38">
+        <v>1</v>
+      </c>
+      <c r="K49" s="39">
+        <f t="shared" ref="K49" si="20">J49*5</f>
+        <v>5</v>
+      </c>
+      <c r="L49" s="38"/>
+    </row>
+    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="50">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
       <c r="C50" s="56" t="s">
-        <v>405</v>
-      </c>
-      <c r="D50" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="D50" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="37" t="s">
+      <c r="E50" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="F50" s="36" t="s">
+      <c r="F50" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="G50" s="37"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="37" t="s">
-        <v>380</v>
-      </c>
-      <c r="K50" s="36"/>
-      <c r="L50" s="36">
+      <c r="G50" s="65" t="s">
+        <v>377</v>
+      </c>
+      <c r="H50" s="64" t="s">
+        <v>408</v>
+      </c>
+      <c r="I50" s="65" t="s">
+        <v>408</v>
+      </c>
+      <c r="J50" s="64">
         <v>8</v>
       </c>
-      <c r="M50" s="37">
-        <f>L50*5</f>
+      <c r="K50" s="65">
+        <f>J50*5</f>
         <v>40</v>
       </c>
-      <c r="N50" s="36"/>
-    </row>
-    <row r="51" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L50" s="64"/>
+    </row>
+    <row r="51" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="50">
         <f t="shared" si="0"/>
@@ -3983,24 +3829,22 @@
       <c r="G51" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="H51" s="38"/>
-      <c r="I51" s="38" t="s">
+      <c r="H51" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="J51" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="K51" s="38"/>
-      <c r="L51" s="38">
-        <v>1</v>
-      </c>
-      <c r="M51" s="39">
-        <f t="shared" ref="M51" si="21">L51*5</f>
-        <v>5</v>
-      </c>
-      <c r="N51" s="38"/>
-    </row>
-    <row r="52" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I51" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J51" s="38">
+        <v>1</v>
+      </c>
+      <c r="K51" s="39">
+        <f t="shared" ref="K51" si="21">J51*5</f>
+        <v>5</v>
+      </c>
+      <c r="L51" s="38"/>
+    </row>
+    <row r="52" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="50">
         <f>ROW(B52) - ROW($B$9)</f>
@@ -4021,24 +3865,22 @@
       <c r="G52" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36" t="s">
+      <c r="H52" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="J52" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="K52" s="36"/>
-      <c r="L52" s="36">
-        <v>1</v>
-      </c>
-      <c r="M52" s="37">
-        <f>L52*5</f>
-        <v>5</v>
-      </c>
-      <c r="N52" s="36"/>
-    </row>
-    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I52" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J52" s="36">
+        <v>1</v>
+      </c>
+      <c r="K52" s="37">
+        <f>J52*5</f>
+        <v>5</v>
+      </c>
+      <c r="L52" s="36"/>
+    </row>
+    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="50">
         <f t="shared" si="0"/>
@@ -4059,24 +3901,22 @@
       <c r="G53" s="39" t="s">
         <v>284</v>
       </c>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38" t="s">
+      <c r="H53" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="J53" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38">
+      <c r="I53" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J53" s="38">
         <v>3</v>
       </c>
-      <c r="M53" s="39">
-        <f t="shared" ref="M53" si="22">L53*5</f>
+      <c r="K53" s="39">
+        <f t="shared" ref="K53" si="22">J53*5</f>
         <v>15</v>
       </c>
-      <c r="N53" s="38"/>
-    </row>
-    <row r="54" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L53" s="38"/>
+    </row>
+    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="50">
         <f>ROW(B54) - ROW($B$9)</f>
@@ -4097,24 +3937,22 @@
       <c r="G54" s="37" t="s">
         <v>285</v>
       </c>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36" t="s">
+      <c r="H54" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="J54" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="K54" s="36"/>
-      <c r="L54" s="36">
+      <c r="I54" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="J54" s="36">
         <v>2</v>
       </c>
-      <c r="M54" s="37">
-        <f>L54*5</f>
+      <c r="K54" s="37">
+        <f>J54*5</f>
         <v>10</v>
       </c>
-      <c r="N54" s="36"/>
-    </row>
-    <row r="55" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L54" s="36"/>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="50">
         <f t="shared" si="0"/>
@@ -4135,24 +3973,22 @@
       <c r="G55" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38" t="s">
+      <c r="H55" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J55" s="39" t="s">
-        <v>382</v>
-      </c>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38">
+      <c r="I55" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="J55" s="38">
         <v>6</v>
       </c>
-      <c r="M55" s="39">
-        <f t="shared" ref="M55" si="23">L55*5</f>
+      <c r="K55" s="39">
+        <f t="shared" ref="K55" si="23">J55*5</f>
         <v>30</v>
       </c>
-      <c r="N55" s="38"/>
-    </row>
-    <row r="56" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L55" s="38"/>
+    </row>
+    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="50">
         <f>ROW(B56) - ROW($B$9)</f>
@@ -4173,24 +4009,22 @@
       <c r="G56" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36" t="s">
+      <c r="H56" s="36" t="s">
         <v>345</v>
       </c>
-      <c r="J56" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36">
-        <v>1</v>
-      </c>
-      <c r="M56" s="37">
-        <f>L56*5</f>
-        <v>5</v>
-      </c>
-      <c r="N56" s="36"/>
-    </row>
-    <row r="57" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I56" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="J56" s="36">
+        <v>1</v>
+      </c>
+      <c r="K56" s="37">
+        <f>J56*5</f>
+        <v>5</v>
+      </c>
+      <c r="L56" s="36"/>
+    </row>
+    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="50">
         <f t="shared" si="0"/>
@@ -4211,24 +4045,22 @@
       <c r="G57" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38" t="s">
+      <c r="H57" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J57" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="K57" s="38"/>
-      <c r="L57" s="38">
-        <v>5</v>
-      </c>
-      <c r="M57" s="39">
-        <f t="shared" ref="M57" si="24">L57*5</f>
+      <c r="I57" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="J57" s="38">
+        <v>5</v>
+      </c>
+      <c r="K57" s="39">
+        <f t="shared" ref="K57" si="24">J57*5</f>
         <v>25</v>
       </c>
-      <c r="N57" s="38"/>
-    </row>
-    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L57" s="38"/>
+    </row>
+    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="50">
         <f>ROW(B58) - ROW($B$9)</f>
@@ -4249,24 +4081,22 @@
       <c r="G58" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36" t="s">
+      <c r="H58" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J58" s="37" t="s">
-        <v>385</v>
-      </c>
-      <c r="K58" s="36"/>
-      <c r="L58" s="36">
-        <v>1</v>
-      </c>
-      <c r="M58" s="37">
-        <f>L58*5</f>
-        <v>5</v>
-      </c>
-      <c r="N58" s="36"/>
-    </row>
-    <row r="59" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="J58" s="36">
+        <v>1</v>
+      </c>
+      <c r="K58" s="37">
+        <f>J58*5</f>
+        <v>5</v>
+      </c>
+      <c r="L58" s="36"/>
+    </row>
+    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="50">
         <f t="shared" si="0"/>
@@ -4287,24 +4117,22 @@
       <c r="G59" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38" t="s">
+      <c r="H59" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J59" s="39" t="s">
-        <v>386</v>
-      </c>
-      <c r="K59" s="38"/>
-      <c r="L59" s="38">
-        <v>1</v>
-      </c>
-      <c r="M59" s="39">
-        <f t="shared" ref="M59" si="25">L59*5</f>
-        <v>5</v>
-      </c>
-      <c r="N59" s="38"/>
-    </row>
-    <row r="60" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="J59" s="38">
+        <v>1</v>
+      </c>
+      <c r="K59" s="39">
+        <f t="shared" ref="K59" si="25">J59*5</f>
+        <v>5</v>
+      </c>
+      <c r="L59" s="38"/>
+    </row>
+    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="50">
         <f>ROW(B60) - ROW($B$9)</f>
@@ -4325,24 +4153,22 @@
       <c r="G60" s="37" t="s">
         <v>291</v>
       </c>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36" t="s">
+      <c r="H60" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J60" s="37" t="s">
-        <v>387</v>
-      </c>
-      <c r="K60" s="36"/>
-      <c r="L60" s="36">
-        <v>1</v>
-      </c>
-      <c r="M60" s="37">
-        <f>L60*5</f>
-        <v>5</v>
-      </c>
-      <c r="N60" s="36"/>
-    </row>
-    <row r="61" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="J60" s="36">
+        <v>1</v>
+      </c>
+      <c r="K60" s="37">
+        <f>J60*5</f>
+        <v>5</v>
+      </c>
+      <c r="L60" s="36"/>
+    </row>
+    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="50">
         <f t="shared" si="0"/>
@@ -4363,24 +4189,22 @@
       <c r="G61" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38" t="s">
+      <c r="H61" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J61" s="39" t="s">
-        <v>388</v>
-      </c>
-      <c r="K61" s="38"/>
-      <c r="L61" s="38">
-        <v>1</v>
-      </c>
-      <c r="M61" s="39">
-        <f t="shared" ref="M61" si="26">L61*5</f>
-        <v>5</v>
-      </c>
-      <c r="N61" s="38"/>
-    </row>
-    <row r="62" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="J61" s="38">
+        <v>1</v>
+      </c>
+      <c r="K61" s="39">
+        <f t="shared" ref="K61" si="26">J61*5</f>
+        <v>5</v>
+      </c>
+      <c r="L61" s="38"/>
+    </row>
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="50">
         <f>ROW(B62) - ROW($B$9)</f>
@@ -4401,24 +4225,22 @@
       <c r="G62" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="H62" s="36"/>
-      <c r="I62" s="36" t="s">
+      <c r="H62" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J62" s="37" t="s">
-        <v>389</v>
-      </c>
-      <c r="K62" s="36"/>
-      <c r="L62" s="36">
+      <c r="I62" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="J62" s="36">
         <v>7</v>
       </c>
-      <c r="M62" s="37">
-        <f>L62*5</f>
+      <c r="K62" s="37">
+        <f>J62*5</f>
         <v>35</v>
       </c>
-      <c r="N62" s="36"/>
-    </row>
-    <row r="63" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L62" s="36"/>
+    </row>
+    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="50">
         <f t="shared" si="0"/>
@@ -4439,24 +4261,22 @@
       <c r="G63" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38" t="s">
+      <c r="H63" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J63" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="K63" s="38"/>
-      <c r="L63" s="38">
+      <c r="I63" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="J63" s="38">
         <v>3</v>
       </c>
-      <c r="M63" s="39">
-        <f t="shared" ref="M63" si="27">L63*5</f>
+      <c r="K63" s="39">
+        <f t="shared" ref="K63" si="27">J63*5</f>
         <v>15</v>
       </c>
-      <c r="N63" s="38"/>
-    </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L63" s="38"/>
+    </row>
+    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="50">
         <f>ROW(B64) - ROW($B$9)</f>
@@ -4477,24 +4297,22 @@
       <c r="G64" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="H64" s="36"/>
-      <c r="I64" s="36" t="s">
+      <c r="H64" s="36" t="s">
         <v>346</v>
       </c>
-      <c r="J64" s="37" t="s">
-        <v>391</v>
-      </c>
-      <c r="K64" s="36"/>
-      <c r="L64" s="36">
-        <v>1</v>
-      </c>
-      <c r="M64" s="37">
-        <f>L64*5</f>
-        <v>5</v>
-      </c>
-      <c r="N64" s="36"/>
-    </row>
-    <row r="65" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I64" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="J64" s="36">
+        <v>1</v>
+      </c>
+      <c r="K64" s="37">
+        <f>J64*5</f>
+        <v>5</v>
+      </c>
+      <c r="L64" s="36"/>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="50">
         <f t="shared" si="0"/>
@@ -4515,24 +4333,22 @@
       <c r="G65" s="39" t="s">
         <v>296</v>
       </c>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38" t="s">
+      <c r="H65" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J65" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="K65" s="38"/>
-      <c r="L65" s="38">
+      <c r="I65" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="J65" s="38">
         <v>2</v>
       </c>
-      <c r="M65" s="39">
-        <f t="shared" ref="M65" si="28">L65*5</f>
+      <c r="K65" s="39">
+        <f t="shared" ref="K65" si="28">J65*5</f>
         <v>10</v>
       </c>
-      <c r="N65" s="38"/>
-    </row>
-    <row r="66" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L65" s="38"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="50">
         <f>ROW(B66) - ROW($B$9)</f>
@@ -4553,24 +4369,22 @@
       <c r="G66" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="H66" s="36"/>
-      <c r="I66" s="36" t="s">
+      <c r="H66" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J66" s="37" t="s">
-        <v>393</v>
-      </c>
-      <c r="K66" s="36"/>
-      <c r="L66" s="36">
-        <v>1</v>
-      </c>
-      <c r="M66" s="37">
-        <f>L66*5</f>
-        <v>5</v>
-      </c>
-      <c r="N66" s="36"/>
-    </row>
-    <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I66" s="37" t="s">
+        <v>390</v>
+      </c>
+      <c r="J66" s="36">
+        <v>1</v>
+      </c>
+      <c r="K66" s="37">
+        <f>J66*5</f>
+        <v>5</v>
+      </c>
+      <c r="L66" s="36"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="50">
         <f t="shared" si="0"/>
@@ -4591,24 +4405,22 @@
       <c r="G67" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38" t="s">
+      <c r="H67" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J67" s="39" t="s">
-        <v>394</v>
-      </c>
-      <c r="K67" s="38"/>
-      <c r="L67" s="38">
-        <v>1</v>
-      </c>
-      <c r="M67" s="39">
-        <f t="shared" ref="M67" si="29">L67*5</f>
-        <v>5</v>
-      </c>
-      <c r="N67" s="38"/>
-    </row>
-    <row r="68" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I67" s="39" t="s">
+        <v>391</v>
+      </c>
+      <c r="J67" s="38">
+        <v>1</v>
+      </c>
+      <c r="K67" s="39">
+        <f t="shared" ref="K67" si="29">J67*5</f>
+        <v>5</v>
+      </c>
+      <c r="L67" s="38"/>
+    </row>
+    <row r="68" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="50">
         <f>ROW(B68) - ROW($B$9)</f>
@@ -4629,24 +4441,22 @@
       <c r="G68" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36" t="s">
+      <c r="H68" s="36" t="s">
         <v>347</v>
       </c>
-      <c r="J68" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="K68" s="36"/>
-      <c r="L68" s="36">
-        <v>1</v>
-      </c>
-      <c r="M68" s="37">
-        <f>L68*5</f>
-        <v>5</v>
-      </c>
-      <c r="N68" s="36"/>
-    </row>
-    <row r="69" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I68" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="J68" s="36">
+        <v>1</v>
+      </c>
+      <c r="K68" s="37">
+        <f>J68*5</f>
+        <v>5</v>
+      </c>
+      <c r="L68" s="36"/>
+    </row>
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="50">
         <f t="shared" si="0"/>
@@ -4667,24 +4477,22 @@
       <c r="G69" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38" t="s">
+      <c r="H69" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J69" s="39" t="s">
-        <v>396</v>
-      </c>
-      <c r="K69" s="38"/>
-      <c r="L69" s="38">
-        <v>1</v>
-      </c>
-      <c r="M69" s="39">
-        <f t="shared" ref="M69" si="30">L69*5</f>
-        <v>5</v>
-      </c>
-      <c r="N69" s="38"/>
-    </row>
-    <row r="70" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I69" s="39" t="s">
+        <v>393</v>
+      </c>
+      <c r="J69" s="38">
+        <v>1</v>
+      </c>
+      <c r="K69" s="39">
+        <f t="shared" ref="K69" si="30">J69*5</f>
+        <v>5</v>
+      </c>
+      <c r="L69" s="38"/>
+    </row>
+    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="50">
         <f>ROW(B70) - ROW($B$9)</f>
@@ -4705,24 +4513,22 @@
       <c r="G70" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36" t="s">
+      <c r="H70" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J70" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="K70" s="36"/>
-      <c r="L70" s="36">
-        <v>1</v>
-      </c>
-      <c r="M70" s="37">
-        <f>L70*5</f>
-        <v>5</v>
-      </c>
-      <c r="N70" s="36"/>
-    </row>
-    <row r="71" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I70" s="37" t="s">
+        <v>394</v>
+      </c>
+      <c r="J70" s="36">
+        <v>1</v>
+      </c>
+      <c r="K70" s="37">
+        <f>J70*5</f>
+        <v>5</v>
+      </c>
+      <c r="L70" s="36"/>
+    </row>
+    <row r="71" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="50">
         <f t="shared" si="0"/>
@@ -4743,24 +4549,22 @@
       <c r="G71" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="H71" s="38"/>
-      <c r="I71" s="38" t="s">
+      <c r="H71" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J71" s="39" t="s">
-        <v>398</v>
-      </c>
-      <c r="K71" s="38"/>
-      <c r="L71" s="38">
-        <v>1</v>
-      </c>
-      <c r="M71" s="39">
-        <f t="shared" ref="M71" si="31">L71*5</f>
-        <v>5</v>
-      </c>
-      <c r="N71" s="38"/>
-    </row>
-    <row r="72" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I71" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="J71" s="38">
+        <v>1</v>
+      </c>
+      <c r="K71" s="39">
+        <f t="shared" ref="K71" si="31">J71*5</f>
+        <v>5</v>
+      </c>
+      <c r="L71" s="38"/>
+    </row>
+    <row r="72" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="50">
         <f>ROW(B72) - ROW($B$9)</f>
@@ -4781,24 +4585,22 @@
       <c r="G72" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="H72" s="36"/>
-      <c r="I72" s="36" t="s">
+      <c r="H72" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J72" s="37" t="s">
-        <v>399</v>
-      </c>
-      <c r="K72" s="36"/>
-      <c r="L72" s="36">
-        <v>1</v>
-      </c>
-      <c r="M72" s="37">
-        <f>L72*5</f>
-        <v>5</v>
-      </c>
-      <c r="N72" s="36"/>
-    </row>
-    <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I72" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="J72" s="36">
+        <v>1</v>
+      </c>
+      <c r="K72" s="37">
+        <f>J72*5</f>
+        <v>5</v>
+      </c>
+      <c r="L72" s="36"/>
+    </row>
+    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="50">
         <f t="shared" si="0"/>
@@ -4819,24 +4621,22 @@
       <c r="G73" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38" t="s">
+      <c r="H73" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J73" s="39" t="s">
-        <v>400</v>
-      </c>
-      <c r="K73" s="38"/>
-      <c r="L73" s="38">
-        <v>1</v>
-      </c>
-      <c r="M73" s="39">
-        <f t="shared" ref="M73" si="32">L73*5</f>
-        <v>5</v>
-      </c>
-      <c r="N73" s="38"/>
-    </row>
-    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I73" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="J73" s="38">
+        <v>1</v>
+      </c>
+      <c r="K73" s="39">
+        <f t="shared" ref="K73" si="32">J73*5</f>
+        <v>5</v>
+      </c>
+      <c r="L73" s="38"/>
+    </row>
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="50">
         <f>ROW(B74) - ROW($B$9)</f>
@@ -4857,24 +4657,22 @@
       <c r="G74" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36" t="s">
+      <c r="H74" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J74" s="37" t="s">
-        <v>401</v>
-      </c>
-      <c r="K74" s="36"/>
-      <c r="L74" s="36">
+      <c r="I74" s="37" t="s">
+        <v>398</v>
+      </c>
+      <c r="J74" s="36">
         <v>7</v>
       </c>
-      <c r="M74" s="37">
-        <f>L74*5</f>
+      <c r="K74" s="37">
+        <f>J74*5</f>
         <v>35</v>
       </c>
-      <c r="N74" s="36"/>
-    </row>
-    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L74" s="36"/>
+    </row>
+    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="50">
         <f t="shared" si="0"/>
@@ -4895,24 +4693,22 @@
       <c r="G75" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38" t="s">
+      <c r="H75" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="J75" s="39" t="s">
-        <v>402</v>
-      </c>
-      <c r="K75" s="38"/>
-      <c r="L75" s="38">
-        <v>1</v>
-      </c>
-      <c r="M75" s="39">
-        <f t="shared" ref="M75" si="33">L75*5</f>
-        <v>5</v>
-      </c>
-      <c r="N75" s="38"/>
-    </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I75" s="39" t="s">
+        <v>399</v>
+      </c>
+      <c r="J75" s="38">
+        <v>1</v>
+      </c>
+      <c r="K75" s="39">
+        <f t="shared" ref="K75" si="33">J75*5</f>
+        <v>5</v>
+      </c>
+      <c r="L75" s="38"/>
+    </row>
+    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="50">
         <f>ROW(B76) - ROW($B$9)</f>
@@ -4933,24 +4729,22 @@
       <c r="G76" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="H76" s="36"/>
-      <c r="I76" s="36" t="s">
+      <c r="H76" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="J76" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="K76" s="36"/>
-      <c r="L76" s="36">
-        <v>1</v>
-      </c>
-      <c r="M76" s="37">
-        <f>L76*5</f>
-        <v>5</v>
-      </c>
-      <c r="N76" s="36"/>
-    </row>
-    <row r="77" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I76" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="J76" s="36">
+        <v>1</v>
+      </c>
+      <c r="K76" s="37">
+        <f>J76*5</f>
+        <v>5</v>
+      </c>
+      <c r="L76" s="36"/>
+    </row>
+    <row r="77" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="50">
         <f t="shared" si="0"/>
@@ -4971,24 +4765,22 @@
       <c r="G77" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38" t="s">
+      <c r="H77" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="J77" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="K77" s="38"/>
-      <c r="L77" s="38">
-        <v>1</v>
-      </c>
-      <c r="M77" s="39">
-        <f t="shared" ref="M77" si="34">L77*5</f>
-        <v>5</v>
-      </c>
-      <c r="N77" s="38"/>
-    </row>
-    <row r="78" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I77" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J77" s="38">
+        <v>1</v>
+      </c>
+      <c r="K77" s="39">
+        <f t="shared" ref="K77" si="34">J77*5</f>
+        <v>5</v>
+      </c>
+      <c r="L77" s="38"/>
+    </row>
+    <row r="78" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="50">
         <f>ROW(B78) - ROW($B$9)</f>
@@ -5009,24 +4801,22 @@
       <c r="G78" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36" t="s">
+      <c r="H78" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="J78" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="K78" s="36"/>
-      <c r="L78" s="36">
+      <c r="I78" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J78" s="36">
         <v>2</v>
       </c>
-      <c r="M78" s="37">
-        <f>L78*5</f>
+      <c r="K78" s="37">
+        <f>J78*5</f>
         <v>10</v>
       </c>
-      <c r="N78" s="36"/>
-    </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L78" s="36"/>
+    </row>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="50">
         <f t="shared" si="0"/>
@@ -5047,24 +4837,22 @@
       <c r="G79" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38" t="s">
+      <c r="H79" s="38" t="s">
         <v>349</v>
       </c>
-      <c r="J79" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="K79" s="38"/>
-      <c r="L79" s="38">
-        <v>1</v>
-      </c>
-      <c r="M79" s="39">
-        <f t="shared" ref="M79" si="35">L79*5</f>
-        <v>5</v>
-      </c>
-      <c r="N79" s="38"/>
-    </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I79" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J79" s="38">
+        <v>1</v>
+      </c>
+      <c r="K79" s="39">
+        <f t="shared" ref="K79" si="35">J79*5</f>
+        <v>5</v>
+      </c>
+      <c r="L79" s="38"/>
+    </row>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="50">
         <f>ROW(B80) - ROW($B$9)</f>
@@ -5085,24 +4873,22 @@
       <c r="G80" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36" t="s">
+      <c r="H80" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="J80" s="37" t="s">
-        <v>308</v>
-      </c>
-      <c r="K80" s="36"/>
-      <c r="L80" s="36">
-        <v>1</v>
-      </c>
-      <c r="M80" s="37">
-        <f>L80*5</f>
-        <v>5</v>
-      </c>
-      <c r="N80" s="36"/>
-    </row>
-    <row r="81" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I80" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J80" s="36">
+        <v>1</v>
+      </c>
+      <c r="K80" s="37">
+        <f>J80*5</f>
+        <v>5</v>
+      </c>
+      <c r="L80" s="36"/>
+    </row>
+    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="50">
         <f t="shared" si="0"/>
@@ -5123,24 +4909,22 @@
       <c r="G81" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38" t="s">
+      <c r="H81" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="J81" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="K81" s="38"/>
-      <c r="L81" s="38">
-        <v>1</v>
-      </c>
-      <c r="M81" s="39">
-        <f t="shared" ref="M81" si="36">L81*5</f>
-        <v>5</v>
-      </c>
-      <c r="N81" s="38"/>
-    </row>
-    <row r="82" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I81" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J81" s="38">
+        <v>1</v>
+      </c>
+      <c r="K81" s="39">
+        <f t="shared" ref="K81" si="36">J81*5</f>
+        <v>5</v>
+      </c>
+      <c r="L81" s="38"/>
+    </row>
+    <row r="82" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="50">
         <f>ROW(B82) - ROW($B$9)</f>
@@ -5161,24 +4945,22 @@
       <c r="G82" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="H82" s="36"/>
-      <c r="I82" s="36" t="s">
+      <c r="H82" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="J82" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="K82" s="36"/>
-      <c r="L82" s="36">
-        <v>1</v>
-      </c>
-      <c r="M82" s="37">
-        <f>L82*5</f>
-        <v>5</v>
-      </c>
-      <c r="N82" s="36"/>
-    </row>
-    <row r="83" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I82" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J82" s="36">
+        <v>1</v>
+      </c>
+      <c r="K82" s="37">
+        <f>J82*5</f>
+        <v>5</v>
+      </c>
+      <c r="L82" s="36"/>
+    </row>
+    <row r="83" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="50">
         <f t="shared" si="0"/>
@@ -5199,24 +4981,22 @@
       <c r="G83" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38" t="s">
+      <c r="H83" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="J83" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="K83" s="38"/>
-      <c r="L83" s="38">
-        <v>1</v>
-      </c>
-      <c r="M83" s="39">
-        <f t="shared" ref="M83" si="37">L83*5</f>
-        <v>5</v>
-      </c>
-      <c r="N83" s="38"/>
-    </row>
-    <row r="84" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I83" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J83" s="38">
+        <v>1</v>
+      </c>
+      <c r="K83" s="39">
+        <f t="shared" ref="K83" si="37">J83*5</f>
+        <v>5</v>
+      </c>
+      <c r="L83" s="38"/>
+    </row>
+    <row r="84" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="50">
         <f>ROW(B84) - ROW($B$9)</f>
@@ -5237,24 +5017,22 @@
       <c r="G84" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="H84" s="36"/>
-      <c r="I84" s="36" t="s">
+      <c r="H84" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="J84" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="K84" s="36"/>
-      <c r="L84" s="36">
-        <v>1</v>
-      </c>
-      <c r="M84" s="37">
-        <f>L84*5</f>
-        <v>5</v>
-      </c>
-      <c r="N84" s="36"/>
-    </row>
-    <row r="85" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I84" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J84" s="36">
+        <v>1</v>
+      </c>
+      <c r="K84" s="37">
+        <f>J84*5</f>
+        <v>5</v>
+      </c>
+      <c r="L84" s="36"/>
+    </row>
+    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="50">
         <f t="shared" si="0"/>
@@ -5275,24 +5053,22 @@
       <c r="G85" s="39" t="s">
         <v>313</v>
       </c>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38" t="s">
+      <c r="H85" s="38" t="s">
         <v>353</v>
       </c>
-      <c r="J85" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="K85" s="38"/>
-      <c r="L85" s="38">
-        <v>1</v>
-      </c>
-      <c r="M85" s="39">
-        <f t="shared" ref="M85" si="38">L85*5</f>
-        <v>5</v>
-      </c>
-      <c r="N85" s="38"/>
-    </row>
-    <row r="86" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I85" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J85" s="38">
+        <v>1</v>
+      </c>
+      <c r="K85" s="39">
+        <f t="shared" ref="K85" si="38">J85*5</f>
+        <v>5</v>
+      </c>
+      <c r="L85" s="38"/>
+    </row>
+    <row r="86" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="50">
         <f>ROW(B86) - ROW($B$9)</f>
@@ -5313,24 +5089,22 @@
       <c r="G86" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="H86" s="36"/>
-      <c r="I86" s="36" t="s">
+      <c r="H86" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="J86" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K86" s="36"/>
-      <c r="L86" s="36">
-        <v>1</v>
-      </c>
-      <c r="M86" s="37">
-        <f>L86*5</f>
-        <v>5</v>
-      </c>
-      <c r="N86" s="36"/>
-    </row>
-    <row r="87" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I86" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J86" s="36">
+        <v>1</v>
+      </c>
+      <c r="K86" s="37">
+        <f>J86*5</f>
+        <v>5</v>
+      </c>
+      <c r="L86" s="36"/>
+    </row>
+    <row r="87" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="50">
         <f t="shared" si="0"/>
@@ -5351,24 +5125,22 @@
       <c r="G87" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="H87" s="38"/>
-      <c r="I87" s="38" t="s">
+      <c r="H87" s="38" t="s">
         <v>348</v>
       </c>
-      <c r="J87" s="39" t="s">
-        <v>315</v>
-      </c>
-      <c r="K87" s="38"/>
-      <c r="L87" s="38">
-        <v>1</v>
-      </c>
-      <c r="M87" s="39">
-        <f t="shared" ref="M87" si="39">L87*5</f>
-        <v>5</v>
-      </c>
-      <c r="N87" s="38"/>
-    </row>
-    <row r="88" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I87" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J87" s="38">
+        <v>1</v>
+      </c>
+      <c r="K87" s="39">
+        <f t="shared" ref="K87" si="39">J87*5</f>
+        <v>5</v>
+      </c>
+      <c r="L87" s="38"/>
+    </row>
+    <row r="88" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="50">
         <f>ROW(B88) - ROW($B$9)</f>
@@ -5389,24 +5161,22 @@
       <c r="G88" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="H88" s="36"/>
-      <c r="I88" s="36" t="s">
+      <c r="H88" s="36" t="s">
         <v>353</v>
       </c>
-      <c r="J88" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="K88" s="36"/>
-      <c r="L88" s="36">
-        <v>1</v>
-      </c>
-      <c r="M88" s="37">
-        <f>L88*5</f>
-        <v>5</v>
-      </c>
-      <c r="N88" s="36"/>
-    </row>
-    <row r="89" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I88" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J88" s="36">
+        <v>1</v>
+      </c>
+      <c r="K88" s="37">
+        <f>J88*5</f>
+        <v>5</v>
+      </c>
+      <c r="L88" s="36"/>
+    </row>
+    <row r="89" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="50">
         <f t="shared" si="0"/>
@@ -5427,24 +5197,22 @@
       <c r="G89" s="39" t="s">
         <v>317</v>
       </c>
-      <c r="H89" s="38"/>
-      <c r="I89" s="38" t="s">
+      <c r="H89" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="J89" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="K89" s="38"/>
-      <c r="L89" s="38">
-        <v>1</v>
-      </c>
-      <c r="M89" s="39">
-        <f t="shared" ref="M89" si="40">L89*5</f>
-        <v>5</v>
-      </c>
-      <c r="N89" s="38"/>
-    </row>
-    <row r="90" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I89" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J89" s="38">
+        <v>1</v>
+      </c>
+      <c r="K89" s="39">
+        <f t="shared" ref="K89" si="40">J89*5</f>
+        <v>5</v>
+      </c>
+      <c r="L89" s="38"/>
+    </row>
+    <row r="90" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="50">
         <f>ROW(B90) - ROW($B$9)</f>
@@ -5465,24 +5233,22 @@
       <c r="G90" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="H90" s="36"/>
-      <c r="I90" s="36" t="s">
+      <c r="H90" s="36" t="s">
         <v>355</v>
       </c>
-      <c r="J90" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="K90" s="36"/>
-      <c r="L90" s="36">
-        <v>1</v>
-      </c>
-      <c r="M90" s="37">
-        <f>L90*5</f>
-        <v>5</v>
-      </c>
-      <c r="N90" s="36"/>
-    </row>
-    <row r="91" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I90" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="J90" s="36">
+        <v>1</v>
+      </c>
+      <c r="K90" s="37">
+        <f>J90*5</f>
+        <v>5</v>
+      </c>
+      <c r="L90" s="36"/>
+    </row>
+    <row r="91" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="50">
         <f t="shared" si="0"/>
@@ -5503,65 +5269,57 @@
       <c r="G91" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="H91" s="38"/>
-      <c r="I91" s="38" t="s">
+      <c r="H91" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="J91" s="39" t="s">
-        <v>403</v>
-      </c>
-      <c r="K91" s="38"/>
-      <c r="L91" s="38">
-        <v>1</v>
-      </c>
-      <c r="M91" s="39">
-        <f t="shared" ref="M91:M92" si="41">L91*5</f>
-        <v>5</v>
-      </c>
-      <c r="N91" s="38"/>
-    </row>
-    <row r="92" spans="1:14" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I91" s="39" t="s">
+        <v>400</v>
+      </c>
+      <c r="J91" s="38">
+        <v>1</v>
+      </c>
+      <c r="K91" s="39">
+        <f t="shared" ref="K91:K92" si="41">J91*5</f>
+        <v>5</v>
+      </c>
+      <c r="L91" s="38"/>
+    </row>
+    <row r="92" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="58">
         <v>83</v>
       </c>
       <c r="C92" s="57" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D92" s="38" t="s">
-        <v>413</v>
-      </c>
-      <c r="E92" s="38" t="s">
-        <v>414</v>
+        <v>408</v>
+      </c>
+      <c r="E92" s="39" t="s">
+        <v>409</v>
       </c>
       <c r="F92" s="38" t="s">
-        <v>413</v>
-      </c>
-      <c r="G92" s="38" t="s">
-        <v>415</v>
-      </c>
-      <c r="H92" s="63" t="s">
-        <v>413</v>
-      </c>
-      <c r="I92" s="66" t="s">
-        <v>413</v>
-      </c>
-      <c r="J92" s="66" t="s">
-        <v>413</v>
-      </c>
-      <c r="K92" s="67" t="s">
-        <v>417</v>
-      </c>
-      <c r="L92" s="66">
-        <v>1</v>
-      </c>
-      <c r="M92" s="66">
+        <v>408</v>
+      </c>
+      <c r="G92" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="H92" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="I92" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="J92" s="38">
+        <v>1</v>
+      </c>
+      <c r="K92" s="39">
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="N92" s="59"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L92" s="38"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="31"/>
       <c r="C93" s="48"/>
@@ -5569,15 +5327,13 @@
       <c r="E93" s="33"/>
       <c r="F93" s="34"/>
       <c r="G93" s="35"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="64"/>
-      <c r="J93" s="65"/>
-      <c r="K93" s="35"/>
-      <c r="L93" s="65"/>
-      <c r="M93" s="65"/>
-      <c r="N93" s="41"/>
-    </row>
-    <row r="94" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="59"/>
+      <c r="I93" s="60"/>
+      <c r="J93" s="60"/>
+      <c r="K93" s="60"/>
+      <c r="L93" s="41"/>
+    </row>
+    <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="24"/>
       <c r="C94" s="49"/>
@@ -5589,20 +5345,15 @@
       <c r="I94" s="9"/>
       <c r="J94" s="9"/>
       <c r="K94" s="9"/>
-      <c r="L94" s="9"/>
-      <c r="M94" s="9"/>
-      <c r="N94" s="42"/>
+      <c r="L94" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="N3:N8"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="L3:L8"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="K92" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Design Files/Remote_Sensor_Unit/BOM/Client_BOM_Remote_Sensor_Unit.xlsx
+++ b/Design Files/Remote_Sensor_Unit/BOM/Client_BOM_Remote_Sensor_Unit.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="417">
   <si>
     <t>Component list</t>
   </si>
@@ -1255,6 +1255,21 @@
   </si>
   <si>
     <t>Bill of Materials for Project [Remote_Sensor_Unit]</t>
+  </si>
+  <si>
+    <t>Refrence Link</t>
+  </si>
+  <si>
+    <t>USB A to A Cable</t>
+  </si>
+  <si>
+    <t>LC-2030C</t>
+  </si>
+  <si>
+    <t>3m - Cable/ModularCable ROHS</t>
+  </si>
+  <si>
+    <t>C type Adopter</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1279,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1399,6 +1414,14 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1639,10 +1662,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1803,6 +1827,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1812,14 +1842,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2159,7 +2187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2185,10 +2213,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2224,7 +2252,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="62"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2242,7 +2270,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="63"/>
+      <c r="L4" s="65"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2260,7 +2288,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="63"/>
+      <c r="L5" s="65"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2274,7 +2302,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="63"/>
+      <c r="L6" s="65"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2288,7 +2316,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="63"/>
+      <c r="L7" s="65"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2302,7 +2330,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="63"/>
+      <c r="L8" s="65"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2349,26 +2377,26 @@
       <c r="C10" s="56" t="s">
         <v>357</v>
       </c>
-      <c r="D10" s="64" t="s">
+      <c r="D10" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="64" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="G10" s="65"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="65" t="s">
-        <v>408</v>
-      </c>
-      <c r="J10" s="64">
-        <v>1</v>
-      </c>
-      <c r="K10" s="65">
+      <c r="G10" s="62"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="J10" s="61">
+        <v>1</v>
+      </c>
+      <c r="K10" s="62">
         <f>J10*5</f>
         <v>5</v>
       </c>
-      <c r="L10" s="64"/>
+      <c r="L10" s="61"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -3781,32 +3809,32 @@
       <c r="C50" s="56" t="s">
         <v>402</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="E50" s="65" t="s">
+      <c r="E50" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="F50" s="64" t="s">
+      <c r="F50" s="61" t="s">
         <v>225</v>
       </c>
-      <c r="G50" s="65" t="s">
+      <c r="G50" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="H50" s="64" t="s">
-        <v>408</v>
-      </c>
-      <c r="I50" s="65" t="s">
-        <v>408</v>
-      </c>
-      <c r="J50" s="64">
+      <c r="H50" s="61" t="s">
+        <v>408</v>
+      </c>
+      <c r="I50" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="J50" s="61">
         <v>8</v>
       </c>
-      <c r="K50" s="65">
+      <c r="K50" s="62">
         <f>J50*5</f>
         <v>40</v>
       </c>
-      <c r="L50" s="64"/>
+      <c r="L50" s="61"/>
     </row>
     <row r="51" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -5279,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="K91" s="39">
-        <f t="shared" ref="K91:K92" si="41">J91*5</f>
+        <f t="shared" ref="K91:K94" si="41">J91*5</f>
         <v>5</v>
       </c>
       <c r="L91" s="38"/>
@@ -5319,41 +5347,154 @@
       </c>
       <c r="L92" s="38"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="48"/>
-      <c r="D93" s="32"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="60"/>
-      <c r="J93" s="60"/>
-      <c r="K93" s="60"/>
-      <c r="L93" s="41"/>
+      <c r="B93" s="58">
+        <v>84</v>
+      </c>
+      <c r="C93" s="57" t="s">
+        <v>407</v>
+      </c>
+      <c r="D93" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="E93" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F93" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="G93" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="H93" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="I93" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="J93" s="38">
+        <v>1</v>
+      </c>
+      <c r="K93" s="39">
+        <f t="shared" si="41"/>
+        <v>5</v>
+      </c>
+      <c r="L93" s="66" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="24"/>
-      <c r="C94" s="49"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="9"/>
-      <c r="L94" s="42"/>
+      <c r="B94" s="58">
+        <v>85</v>
+      </c>
+      <c r="C94" s="57" t="s">
+        <v>407</v>
+      </c>
+      <c r="D94" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="E94" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="G94" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="H94" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="I94" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="J94" s="38">
+        <v>1</v>
+      </c>
+      <c r="K94" s="39">
+        <f t="shared" si="41"/>
+        <v>5</v>
+      </c>
+      <c r="L94" s="66" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="58">
+        <v>86</v>
+      </c>
+      <c r="C95" s="57" t="s">
+        <v>407</v>
+      </c>
+      <c r="D95" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="E95" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="G95" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="H95" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="I95" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="J95" s="38">
+        <v>4</v>
+      </c>
+      <c r="K95" s="39">
+        <f t="shared" ref="K95" si="42">J95*5</f>
+        <v>20</v>
+      </c>
+      <c r="L95" s="38"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="48"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="33"/>
+      <c r="F96" s="34"/>
+      <c r="G96" s="35"/>
+      <c r="H96" s="59"/>
+      <c r="I96" s="60"/>
+      <c r="J96" s="60"/>
+      <c r="K96" s="60"/>
+      <c r="L96" s="41"/>
+    </row>
+    <row r="97" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="49"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
+      <c r="L97" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="L3:L8"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L93" r:id="rId1"/>
+    <hyperlink ref="L94" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
--- a/Design Files/Remote_Sensor_Unit/BOM/Client_BOM_Remote_Sensor_Unit.xlsx
+++ b/Design Files/Remote_Sensor_Unit/BOM/Client_BOM_Remote_Sensor_Unit.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="417">
   <si>
     <t>Component list</t>
   </si>
@@ -1833,6 +1833,9 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1841,9 +1844,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2213,10 +2213,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2252,7 +2252,7 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="64"/>
+      <c r="L3" s="65"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2270,7 +2270,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="65"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2288,7 +2288,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="65"/>
+      <c r="L5" s="66"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2302,7 +2302,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="65"/>
+      <c r="L6" s="66"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2316,7 +2316,7 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="65"/>
+      <c r="L7" s="66"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2330,7 +2330,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="65"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5345,7 +5345,9 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="L92" s="38"/>
+      <c r="L92" s="63" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="93" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -5380,7 +5382,7 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="L93" s="66" t="s">
+      <c r="L93" s="63" t="s">
         <v>412</v>
       </c>
     </row>
@@ -5417,7 +5419,7 @@
         <f t="shared" si="41"/>
         <v>5</v>
       </c>
-      <c r="L94" s="66" t="s">
+      <c r="L94" s="63" t="s">
         <v>412</v>
       </c>
     </row>
@@ -5492,9 +5494,10 @@
   <hyperlinks>
     <hyperlink ref="L93" r:id="rId1"/>
     <hyperlink ref="L94" r:id="rId2"/>
+    <hyperlink ref="L92" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>